--- a/specs/cartes.xlsx
+++ b/specs/cartes.xlsx
@@ -481,9 +481,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -498,9 +496,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-    </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
@@ -515,9 +511,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -539,9 +533,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
@@ -1708,14 +1700,10 @@
       </c>
       <c r="K24" s="6" t="inlineStr">
         <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="L24" s="4" t="inlineStr">
-        <is>
-          <t>buff persistant + limite de munitions non supportes par le moteur actuel</t>
-        </is>
-      </c>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">

--- a/specs/cartes.xlsx
+++ b/specs/cartes.xlsx
@@ -481,7 +481,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -496,7 +495,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
@@ -511,7 +509,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -533,7 +530,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
@@ -1675,7 +1671,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Module Unique</t>
+          <t>Module Principal (deviation du design 'Module Unique', decision utilisateur)</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">

--- a/specs/cartes.xlsx
+++ b/specs/cartes.xlsx
@@ -1536,14 +1536,10 @@
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>cible 'modules de la ligne avant' non representable par CibleCarte (voir specs.md 9.1)</t>
-        </is>
-      </c>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -2236,14 +2232,10 @@
       </c>
       <c r="K36" s="6" t="inlineStr">
         <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="L36" s="4" t="inlineStr">
-        <is>
-          <t>mecanique de detournement de cible non supportee par le moteur actuel</t>
-        </is>
-      </c>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="L36" s="4" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">

--- a/specs/cartes.xlsx
+++ b/specs/cartes.xlsx
@@ -1430,14 +1430,10 @@
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>effet en pourcentage non supporte (la valeur d'une carte est toujours un montant fixe)</t>
-        </is>
-      </c>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -1588,14 +1584,10 @@
       </c>
       <c r="K22" s="6" t="inlineStr">
         <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>cible fixe 'module principal' + effet a duree non supportes par le moteur actuel</t>
-        </is>
-      </c>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -1957,14 +1949,10 @@
       </c>
       <c r="K30" s="6" t="inlineStr">
         <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="L30" s="4" t="inlineStr">
-        <is>
-          <t>gain d'electricite via une carte non supporte par le moteur actuel</t>
-        </is>
-      </c>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">

--- a/specs/cartes.xlsx
+++ b/specs/cartes.xlsx
@@ -1263,14 +1263,10 @@
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>mecanique d'annulation d'attaque non supportee par le moteur actuel (n'est pas un bouclier)</t>
-        </is>
-      </c>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">

--- a/specs/cartes.xlsx
+++ b/specs/cartes.xlsx
@@ -731,7 +731,7 @@
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>Inflige X degats a la colonne ciblee</t>
+          <t>Inflige X degats a une colonne ennemie</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">

--- a/specs/cartes.xlsx
+++ b/specs/cartes.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Legende" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Cartes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Aventures" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cartes'!$A$1:$L$45</definedName>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,6 +41,21 @@
     <font>
       <b val="1"/>
       <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="6">
@@ -87,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -101,6 +117,14 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2674,4 +2698,222 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Registre des aventures - Space Fight</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Brouillon issu des aventures decrites par l'utilisateur (cf. specs.md 2.4 etape 7, contenu</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>encore a specifier completement - pas encore reporte dans specs.md ni implemente).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Colonne Image : fond dedie dans assets/aventure/ (sauvegardes, pas encore branches au code).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Choix 1/2/3 : effet du choix en langage naturel, tel que fourni - pas encore traduit en</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>mecanique de moteur (contrairement a Cartes, aucune colonne Jouable/Effet ici pour l'instant).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Miroir humainement modifiable, comme Cartes - pas relu par le code. Voir CLAUDE.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Nom</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>Choix 1</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>Choix 2</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>Choix 3</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Asteroides</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>assets/aventure/champ_asteroides.png</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Poursuivi par des pirates de l'espace, vous n'avez plus le choix : vaincre ou perir ! A moins que...</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>Traverser le champ d'asteroides - perdez 5 PV sur un de vos modules.
+PUIS ces asteroides n'en finissent plus, perdez encore 5 PV.
+PUIS tout pres de la sortie, vous reperez des debris que vous recuperez (tirer une carte au hasard et la proposer gratuitement au joueur : il la prend ou il passe).</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>Affronter les pirates (lance un combat aleatoire contre 3 ennemis Small).</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr"/>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>Choix 1 : reutilise le tirage de carte gratuit (nouveau : hors flux de recompense standard, carte non ajoutee au deck si le joueur passe). Choix 2 : reutilise creer_flotte, mais avec un nombre/une taille d'ennemis fixes plutot que le tirage habituel lie au niveau (specs.md 2.3/10.3, deja approximatif). Choix 3 vide - a combler ou assumer un choix binaire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Trois lunes</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>assets/aventure/trois_lunes.png</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Un havre de paix au milieu de la galaxie. Aucune forme de vie intelligente, des animaux de taille raisonnable, de l'eau, des fruits et des legumes sauvages partout. Il est temps de faire une pause.</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>Reparer le vaisseau - chaque module regagne 5 PV.</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>Ameliorer - un module gagne 10 PV max (meme montant qu'en Station service).</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>Bricoler - retirer une carte du deck.</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>Choix 1 : nouveau (reparer_module existant ne s'applique qu'a UN module choisi, ici tous les modules a la fois, montant different : 5 au lieu de PV_REPARATION=20). Choix 2 : reutilise ameliorer_module (PV_AMELIORATION=10) sur un module au choix. Choix 3 : nouveau (aucune fonction de retrait de carte cote gameplay actuellement).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Police</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>assets/aventure/police.png</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Pas de bol, votre dernier achat n'est pas aux normes. Et la police de l'espace ne plaisante pas trop dans le coin...</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>Confiscation - supprimer la carte &lt;carte tiree au sort du deck&gt; de votre deck.</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>Mettre aux normes - payez &lt;la moitie du cout de la carte en magasin&gt;.</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>Detourner l'attention - changer la carte (une seule fois).</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>Suppose une carte deja tiree au sort avant meme l'affichage des choix (le texte des choix 1/2 la reference). Choix 2 : "cout de la carte en magasin" suppose la Planete commerciale (prix par carte pas encore definis, specs.md 9.1). Choix 3 : "changer la carte" ambigu - retirer cette carte sans autre effet ? La remplacer par une autre tiree au hasard ? A clarifier.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/specs/cartes.xlsx
+++ b/specs/cartes.xlsx
@@ -2725,6 +2725,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
@@ -2739,6 +2740,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
@@ -2760,6 +2762,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
@@ -2767,6 +2770,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
@@ -2835,7 +2839,7 @@
       <c r="F13" s="10" t="inlineStr"/>
       <c r="G13" s="10" t="inlineStr">
         <is>
-          <t>Choix 1 : reutilise le tirage de carte gratuit (nouveau : hors flux de recompense standard, carte non ajoutee au deck si le joueur passe). Choix 2 : reutilise creer_flotte, mais avec un nombre/une taille d'ennemis fixes plutot que le tirage habituel lie au niveau (specs.md 2.3/10.3, deja approximatif). Choix 3 vide - a combler ou assumer un choix binaire.</t>
+          <t>Decisions prises (voir specs.md 2.5) : sequence en 3 temps sur UN SEUL ecran (bouton Continuer entre chaque etape, pas de fenetres separees) ; module touche par les -5 PV choisi par un clic du joueur ; combat = approximation "3 ennemis tires du pool actuel" (pas de taille S/M/L, absente de config/ennemis.json - implementer ce tag reste une piste ouverte, cf. specs.md 3.2/9.1/10.3, mais pas un prerequis pour cette Aventure). Choix 3 confirme vide (binaire assume).</t>
         </is>
       </c>
     </row>
@@ -2872,7 +2876,7 @@
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>Choix 1 : nouveau (reparer_module existant ne s'applique qu'a UN module choisi, ici tous les modules a la fois, montant different : 5 au lieu de PV_REPARATION=20). Choix 2 : reutilise ameliorer_module (PV_AMELIORATION=10) sur un module au choix. Choix 3 : nouveau (aucune fonction de retrait de carte cote gameplay actuellement).</t>
+          <t>Decisions confirmees (specs.md 2.5) : Reparer = nouveau soin groupe (chaque module +5 PV, distinct de reparer_module qui ne cible qu'un module) ; Ameliorer = reutilise ameliorer_module tel quel sur le module clique ; Bricoler = nouvelle fonction de retrait de carte (aucune n'existe encore, seul ajouter_carte existe).</t>
         </is>
       </c>
     </row>
@@ -2899,17 +2903,17 @@
       </c>
       <c r="E15" s="10" t="inlineStr">
         <is>
-          <t>Mettre aux normes - payez &lt;la moitie du cout de la carte en magasin&gt;.</t>
+          <t>Mettre aux normes - payez 10 Argent (montant fixe, pas un pourcentage du prix en magasin).</t>
         </is>
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
-          <t>Detourner l'attention - changer la carte (une seule fois).</t>
+          <t>Detourner l'attention - tire une seconde carte au hasard qui remplace la premiere, revient a l'ecran avec seulement 2 choix restants (Confiscation/Mettre aux normes).</t>
         </is>
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
-          <t>Suppose une carte deja tiree au sort avant meme l'affichage des choix (le texte des choix 1/2 la reference). Choix 2 : "cout de la carte en magasin" suppose la Planete commerciale (prix par carte pas encore definis, specs.md 9.1). Choix 3 : "changer la carte" ambigu - retirer cette carte sans autre effet ? La remplacer par une autre tiree au hasard ? A clarifier.</t>
+          <t>Decisions prises (specs.md 2.5) : le prix "en magasin" de la carte n'existe pas encore (Planete commerciale non chiffree) -&gt; remplace par un montant fixe de 10 Argent, invente par symetrie avec les autres montants (a ajuster en playtest, meme statut que ARGENT_PAR_ENNEMI_TUE/COUT_ACTION_STATION_SERVICE). "Une seule fois" = une seule fois PAR AVENTURE (pas par run) : rien a persister sur Partie, purement local a l'ecran.</t>
         </is>
       </c>
     </row>

--- a/specs/cartes.xlsx
+++ b/specs/cartes.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Legende" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Cartes" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Aventures" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Ennemis" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cartes'!$A$1:$L$45</definedName>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -56,6 +57,9 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="6">
@@ -103,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -127,6 +131,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2725,7 +2734,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
@@ -2740,7 +2748,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
@@ -2762,7 +2769,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
@@ -2770,7 +2776,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
@@ -2914,6 +2919,445 @@
       <c r="G15" s="10" t="inlineStr">
         <is>
           <t>Decisions prises (specs.md 2.5) : le prix "en magasin" de la carte n'existe pas encore (Planete commerciale non chiffree) -&gt; remplace par un montant fixe de 10 Argent, invente par symetrie avec les autres montants (a ajuster en playtest, meme statut que ARGENT_PAR_ENNEMI_TUE/COUT_ACTION_STATION_SERVICE). "Une seule fois" = une seule fois PAR AVENTURE (pas par run) : rien a persister sur Partie, purement local a l'ecran.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="55" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Registre des ennemis - Space Fight</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Brouillon transcrit depuis une capture d'ecran fournie par l'utilisateur (tableau de conception</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>des ennemis) - remplace les 3 ennemis actuels de config/ennemis.json (ENM_1/2/3, simple "attaque</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>unique X degats", cf. specs.md 3.2). Pas encore implemente : voir la proposition d'implementation</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>donnee a l'utilisateur en meme temps que cet onglet (pas encore reportee dans specs.md).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Deux valeurs incertaines (texte coupe dans la capture d'origine) signalees en Notes : a confirmer</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>aupres de l'utilisateur avant implementation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Colonnes Nom / Taille / Image / Description / PV / X / Y / Actions par tour / Particularites :</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>reprennent telles quelles les donnees de la capture (Image = chemin propose, asset pas encore</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>fourni). Deux colonnes ajoutees, meme convention que l'onglet Cartes :</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>- Jouable : Non pour les 5 (aucune de leurs mecaniques n'existe dans le moteur actuel).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>- Notes : mecanique(s) manquante(s) precisee(s) par ennemi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Miroir humainement modifiable, comme Cartes/Aventures - pas relu par le code. Voir CLAUDE.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>Nom</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Taille</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G20" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>Actions par tour</t>
+        </is>
+      </c>
+      <c r="I20" s="11" t="inlineStr">
+        <is>
+          <t>Particularites</t>
+        </is>
+      </c>
+      <c r="J20" s="11" t="inlineStr">
+        <is>
+          <t>Jouable</t>
+        </is>
+      </c>
+      <c r="K20" s="11" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Pat le Pirate</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>assets/ennemis/pat_le_pirate.png</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>Un pirate qui aime les rimes.</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>50</v>
+      </c>
+      <c r="F21" t="n">
+        <v>5</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="12" t="inlineStr">
+        <is>
+          <t>Inflige X degats en face de lui.</t>
+        </is>
+      </c>
+      <c r="I21" s="12" t="inlineStr">
+        <is>
+          <t>Aucune</t>
+        </is>
+      </c>
+      <c r="J21" s="13" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K21" s="12" t="inlineStr">
+        <is>
+          <t>Aucune mecanique manquante : attaque simple deja supportee (module_cible_par_ennemi + degats_attaque) - drop-in a la place d'un ENM_x actuel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Le nettoyeur</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>assets/ennemis/le_nettoyeur.png</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>Il aime taper fort.</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>25</v>
+      </c>
+      <c r="F22" t="n">
+        <v>7</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" s="12" t="inlineStr">
+        <is>
+          <t>Inflige X degats en face de lui, Y fois.</t>
+        </is>
+      </c>
+      <c r="I22" s="12" t="inlineStr">
+        <is>
+          <t>Toujours a l'arriere derriere un protecteur, si possible.</t>
+        </is>
+      </c>
+      <c r="J22" s="13" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K22" s="12" t="inlineStr">
+        <is>
+          <t>Multi-hit (Y fois par tour) non supporte (Combat._tour_ennemi n'attaque qu'une fois par ennemi). Placement prefere (arriere, protege par un allie devant) non supporte : les positions sont fixees une fois pour toutes a la creation de la flotte, aucune logique de preference/replacement. Particularite retranscrite incomplete (coupee apres "si" dans la capture) - completee ici par symetrie avec Petit Jean, A CONFIRMER aupres de l'utilisateur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Petit Jean</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>assets/ennemis/petit_jean.png</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>Le baleze du coin</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3</v>
+      </c>
+      <c r="H23" s="12" t="inlineStr">
+        <is>
+          <t>Inflige X degats en face de lui.
+Tous les Y tours se met un bouclier de Y.</t>
+        </is>
+      </c>
+      <c r="I23" s="12" t="inlineStr">
+        <is>
+          <t>Toujours a l'avant pour proteger (les autres modules se mettent derriere, si possible).</t>
+        </is>
+      </c>
+      <c r="J23" s="13" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K23" s="12" t="inlineStr">
+        <is>
+          <t>Bouclier ennemi absent du moteur (Ennemi n'a pas de champ bouclier, cf. Ennemi.subir_degats : "pas de bouclier ennemi dans ce POC"). Declenchement periodique (tous les Y tours) non supporte, meme absence pour le multi-hit de Le nettoyeur. Placement prefere (avant, protecteur) non supporte, idem Le nettoyeur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Le puzzle</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>assets/ennemis/le_puzzle.png</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>Eparpille facon puzzle...</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>50</v>
+      </c>
+      <c r="F24" t="n">
+        <v>5</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="12" t="inlineStr">
+        <is>
+          <t>Inflige X degats a tous les ennemis (= tous les modules du joueur).</t>
+        </is>
+      </c>
+      <c r="I24" s="12" t="inlineStr">
+        <is>
+          <t>Aucune</t>
+        </is>
+      </c>
+      <c r="J24" s="13" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K24" s="12" t="inlineStr">
+        <is>
+          <t>Attaque a zone sur tous les modules du joueur non supportee cote ennemi (existe cote joueur, cf. carte Bombardement/Ciel de missiles - meme boucle a reutiliser en sens inverse).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Miroir</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>assets/ennemis/miroir.png</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>Dis moi qui est la plus belle ?</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>50</v>
+      </c>
+      <c r="F25" t="n">
+        <v>5</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="12" t="inlineStr">
+        <is>
+          <t>Pose un "bouclier miroir" de X sur un ennemi de la ligne avant si possible, de la ligne arriere sinon.
+Bouclier miroir = les degats d'un ennemi jusqu'a X lui sont renvoyes (la cible ne subit rien, l'attaquant subit X). Les degats au-dela de X sont geres normalement.
+Exemple bouclier miroir de 5, attaque par M de E pour 8 : M subit 5, E subit 3.</t>
+        </is>
+      </c>
+      <c r="I25" s="12" t="inlineStr">
+        <is>
+          <t>Aucune</t>
+        </is>
+      </c>
+      <c r="J25" s="13" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K25" s="12" t="inlineStr">
+        <is>
+          <t>Cible un module du joueur par preference de colonne (avant sinon arriere) - logique proche des cartes Ligne avant/arriere (specs.md 12.1) mais choisie par IA plutot que cliquee. Bouclier miroir (renvoi de degats a l'attaquant) est un mecanisme entierement nouveau, distinct du bouclier classique/BOUCLIER_PAR_TOUR/Leurre existants - implique qu'un ennemi puisse subir des degats hors carte jouee par le joueur. Dernier chiffre de l'exemple ("E subit ...") coupe dans la capture, complete ici par calcul (8-5=3), A CONFIRMER.</t>
         </is>
       </c>
     </row>

--- a/specs/cartes.xlsx
+++ b/specs/cartes.xlsx
@@ -2956,51 +2956,24 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Brouillon transcrit depuis une capture d'ecran fournie par l'utilisateur (tableau de conception</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>des ennemis) - remplace les 3 ennemis actuels de config/ennemis.json (ENM_1/2/3, simple "attaque</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>unique X degats", cf. specs.md 3.2). Pas encore implemente : voir la proposition d'implementation</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>donnee a l'utilisateur en meme temps que cet onglet (pas encore reportee dans specs.md).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+          <t>Transcrit depuis une capture d'ecran fournie par l'utilisateur (tableau de conception des ennemis) - a remplace les 3 ennemis placeholder de config/ennemis.json (ENM_1/2/3, simple "attaque unique X degats", cf. specs.md 3.2). Desormais implemente (specs.md 13, config/ennemis.json) : les 5 ennemis ci-dessous sont les seuls du jeu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Deux valeurs incertaines (texte coupe dans la capture d'origine) signalees en Notes : a confirmer</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>aupres de l'utilisateur avant implementation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+          <t>Deux valeurs etaient incertaines a la transcription (texte coupe dans la capture d'origine, colonne Notes) : completees par symetrie/calcul lors de l'implementation, cf. Notes de Le nettoyeur et Miroir ci-dessous.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
@@ -3022,22 +2995,20 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>- Jouable : Non pour les 5 (aucune de leurs mecaniques n'existe dans le moteur actuel).</t>
+          <t>- Jouable : Oui pour les 5 (implementees, cf. config/ennemis.json et specs.md 13).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>- Notes : mecanique(s) manquante(s) precisee(s) par ennemi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
+          <t>- Notes : reference a l'implementation (ennemi.py/combat.py/config_poc.py) par ennemi.</t>
+        </is>
+      </c>
+    </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
@@ -3045,7 +3016,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
@@ -3145,12 +3115,12 @@
       </c>
       <c r="J21" s="13" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K21" s="12" t="inlineStr">
         <is>
-          <t>Aucune mecanique manquante : attaque simple deja supportee (module_cible_par_ennemi + degats_attaque) - drop-in a la place d'un ENM_x actuel.</t>
+          <t>Implemente tel quel : attaque de proximite simple (ActionEnnemi type=ATTAQUE, cible=PROXIMITE), cf. specs.md 13.</t>
         </is>
       </c>
     </row>
@@ -3196,12 +3166,12 @@
       </c>
       <c r="J22" s="13" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K22" s="12" t="inlineStr">
         <is>
-          <t>Multi-hit (Y fois par tour) non supporte (Combat._tour_ennemi n'attaque qu'une fois par ennemi). Placement prefere (arriere, protege par un allie devant) non supporte : les positions sont fixees une fois pour toutes a la creation de la flotte, aucune logique de preference/replacement. Particularite retranscrite incomplete (coupee apres "si" dans la capture) - completee ici par symetrie avec Petit Jean, A CONFIRMER aupres de l'utilisateur.</t>
+          <t>Implemente : multi-hit via ActionEnnemi.repetitions=2 ("Y fois" par tour, distinct de la frequence entre tours). Placement prefere (arriere, protege) via SpecEnnemi.placement=PROTEGE_ARRIERE (config_poc._placer_specs_avec_preference). Particularite retranscrite completee par symetrie avec Petit Jean lors de la transcription initiale (texte coupe dans la capture source).</t>
         </is>
       </c>
     </row>
@@ -3248,12 +3218,12 @@
       </c>
       <c r="J23" s="13" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K23" s="12" t="inlineStr">
         <is>
-          <t>Bouclier ennemi absent du moteur (Ennemi n'a pas de champ bouclier, cf. Ennemi.subir_degats : "pas de bouclier ennemi dans ce POC"). Declenchement periodique (tous les Y tours) non supporte, meme absence pour le multi-hit de Le nettoyeur. Placement prefere (avant, protecteur) non supporte, idem Le nettoyeur.</t>
+          <t>Implemente : bouclier ennemi (Ennemi.bouclier/ajouter_bouclier), declenchement periodique via ActionEnnemi.frequence=3/tour_depart=1 (pose 3 bouclier pendant 3 tours, un tour sur trois), placement prefere (avant, protecteur) via SpecEnnemi.placement=PROTECTEUR_AVANT.</t>
         </is>
       </c>
     </row>
@@ -3299,12 +3269,12 @@
       </c>
       <c r="J24" s="13" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K24" s="12" t="inlineStr">
         <is>
-          <t>Attaque a zone sur tous les modules du joueur non supportee cote ennemi (existe cote joueur, cf. carte Bombardement/Ciel de missiles - meme boucle a reutiliser en sens inverse).</t>
+          <t>Implemente : attaque a zone via ActionEnnemi cible=TOUS_MODULES_JOUEUR (Combat._executer_attaque), meme principe que les cartes joueur Bombardement/Ciel de missiles en sens inverse.</t>
         </is>
       </c>
     </row>
@@ -3352,12 +3322,12 @@
       </c>
       <c r="J25" s="13" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K25" s="12" t="inlineStr">
         <is>
-          <t>Cible un module du joueur par preference de colonne (avant sinon arriere) - logique proche des cartes Ligne avant/arriere (specs.md 12.1) mais choisie par IA plutot que cliquee. Bouclier miroir (renvoi de degats a l'attaquant) est un mecanisme entierement nouveau, distinct du bouclier classique/BOUCLIER_PAR_TOUR/Leurre existants - implique qu'un ennemi puisse subir des degats hors carte jouee par le joueur. Dernier chiffre de l'exemple ("E subit ...") coupe dans la capture, complete ici par calcul (8-5=3), A CONFIRMER.</t>
+          <t>Implemente : ActionCarte.BOUCLIER_MIROIR (nouveau type de buff, cf. carte.py) pose sur un module tire au hasard en colonne avant sinon arriere (CibleActionEnnemi.COLONNE_AVANT_SINON_ARRIERE_JOUEUR). Renvoi de degats implemente dans Combat._resoudre_attaque/_consommer_bouclier_miroir : jusqu'a la valeur du bouclier miroir est retiree a l'attaquant, le reste s'applique normalement a la cible - le dernier chiffre de l'exemple, complete par calcul lors de la transcription (8-5=3), est confirme correct par l'implementation.</t>
         </is>
       </c>
     </row>

--- a/specs/cartes.xlsx
+++ b/specs/cartes.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Cartes" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Aventures" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Ennemis" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Modules" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cartes'!$A$1:$L$45</definedName>
@@ -2963,9 +2964,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
@@ -2973,7 +2971,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
@@ -3328,6 +3325,609 @@
       <c r="K25" s="12" t="inlineStr">
         <is>
           <t>Implemente : ActionCarte.BOUCLIER_MIROIR (nouveau type de buff, cf. carte.py) pose sur un module tire au hasard en colonne avant sinon arriere (CibleActionEnnemi.COLONNE_AVANT_SINON_ARRIERE_JOUEUR). Renvoi de degats implemente dans Combat._resoudre_attaque/_consommer_bouclier_miroir : jusqu'a la valeur du bouclier miroir est retiree a l'attaquant, le reste s'applique normalement a la cible - le dernier chiffre de l'exemple, complete par calcul lors de la transcription (8-5=3), est confirme correct par l'implementation.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Registre des modules - Space Fight</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Nouvelles descriptions fournies par l'utilisateur (accroche narrative + indice gameplay par</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>module), reportees dans config/modules.json (description/description_gameplay). Remplace les</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>anciennes descriptions (purement gameplay) des 6 modules deja implementes, et ajoute 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>nouveaux modules (Canon lourd, Controle, Atelier, Radar).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>4 nouveaux modules sans cartes concues pour l'instant (Canon lourd, Controle, Atelier, Radar) :</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>exclus du tirage de choix de module (modules_equipables/specs_equipables, cf. Notes) pour ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>jamais etre proposes/equipes tant qu'ils n'ont pas de deck - sinon plantage au tirage du deck</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>(Deck.piocher_cartes sur une pool vide).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Colonnes Description (accroche affichee a l'ecran de choix de module, specs.md 5) / Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>gameplay (indice sur le type de carte debloque, affiche en plus dans l'infobulle de l'ecran</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Vaisseau) / PV / Nombre de cartes : refletent config/modules.json tel quel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>- Jouable : Oui pour les 6 modules avec des cartes (dont Principal), Non pour les 4 nouveaux</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (pas encore de cartes concues).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>- Notes : etat d'implementation par module.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Miroir humainement modifiable, comme Cartes/Aventures/Ennemis - pas relu par le code. Voir CLAUDE.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Nom</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Description gameplay</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Nb cartes</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Jouable</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>MOD_1</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>assets/modules/principal.png</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>50</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Votre vaisseau, plus cabosse que le Faucon Millenium, mais la prunelle de vos yeux.</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Le coeur du vaisseau : attaque directe, defense et reparation.</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>6</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Module de base, toujours equipe (specs.md 5).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>MOD_2</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Lanceur de missiles</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>assets/modules/missiles.png</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>30</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Tout dans la finesse, des bons vieux missiles qui explosent partout (sauf la ou vous etes, on espere).</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Degats de zone.</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>3</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Implemente, cartes existantes (Ciel de missiles, Missiles groupes, Leurre).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>MOD_3</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Blindage</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>assets/modules/bouclier.png</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>30</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Quand la diplomatie a echoue et qu'on passe a la suite, mieux vaut pouvoir s'abriter.</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Protection des modules via des boucliers.</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Implemente, cartes existantes (Bouclier, Bouclier perpetuel, Blindage maximal, Bouclier adaptatif, Proteger l'avant poste).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>MOD_4</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Generateur</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>assets/modules/generateur.png</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>30</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Une eolienne dans l'espace ? Vous etes sur ?</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Manipulation de l'electricite.</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Implemente, cartes existantes (Surcharge temporaire, Fonds de tiroir).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>MOD_5</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Soute</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>assets/modules/soute.png</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>30</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Une soute bien remplie pour parer a toutes les (mauvaises) surprises...</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Manipulation du deck.</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Implemente, carte existante (Boost).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>MOD_6</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Sabotage</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>assets/modules/sabotage.png</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>30</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Comment ca ton canon est tombe en panne ? C'est marrant parce que le mien non. Regarde...</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Debuffs sur l'ennemi.</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>6</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Implemente, cartes existantes (Tordre le canon, Breche, Ligne avant, Boucliers endommages, Boucliers hors service, Tir allie).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>MOD_7</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Canon lourd</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>assets/modules/canon_lourd.png</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>30</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Ce module envoie du lourd, mieux vaut ne pas se trouver en face.</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Gros degats sur une cible unique.</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Nouveau module (attaque a forte valeur sur cible unique) - aucune carte concue pour l'instant, exclu du tirage (modules_equipables).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>MOD_8</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Controle</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>assets/modules/controle.png</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>30</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>La meilleure facon de se proteger des attaques de l'ennemi, c'est encore de l'empecher de les lancer.</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Controle de l'ennemi (stun...).</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Nouveau module (controle/stun de l'ennemi, specs.md 12.5 - type Controle du moteur, actuellement sans carte) - aucune carte concue, exclu du tirage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>MOD_9</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Atelier</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>assets/modules/atelier.png</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>30</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Bricoler le vaisseau alors que ca tire de tout cote ? Meme pas peur !</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Reparation des modules. Deplacement des modules.</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Nouveau module (reparation/deplacement de modules) - aucune carte concue pour l'instant, exclu du tirage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>MOD_10</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Radar</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>assets/modules/radar.png</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>30</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Quand on connait les points faibles, on peut faire beaucoup plus mal.</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Buffs sur les modules du joueur.</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Nouveau module (buffs sur les modules du joueur) - aucune carte concue pour l'instant, exclu du tirage.</t>
         </is>
       </c>
     </row>

--- a/specs/cartes.xlsx
+++ b/specs/cartes.xlsx
@@ -108,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -137,6 +137,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3339,11 +3340,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Registre des modules - Space Fight</t>
         </is>
@@ -3352,28 +3353,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Nouvelles descriptions fournies par l'utilisateur (accroche narrative + indice gameplay par</t>
+          <t>Descriptions fournies par l'utilisateur (une phrase, accroche narrative par module),</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>module), reportees dans config/modules.json (description/description_gameplay). Remplace les</t>
+          <t>reportees dans config/modules.json (description). Remplace les anciennes descriptions</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>anciennes descriptions (purement gameplay) des 6 modules deja implementes, et ajoute 4</t>
+          <t>(purement gameplay) des 6 modules deja implementes, et ajoute 4 nouveaux modules</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>nouveaux modules (Canon lourd, Controle, Atelier, Radar).</t>
+          <t>(Canon lourd, Controle, Atelier, Radar).</t>
         </is>
       </c>
     </row>
@@ -3408,156 +3409,177 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Colonnes Description (accroche affichee a l'ecran de choix de module, specs.md 5) / Description</t>
+          <t>Colonnes Description (accroche affichee a l'ecran de choix de module et dans l'infobulle de</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>gameplay (indice sur le type de carte debloque, affiche en plus dans l'infobulle de l'ecran</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Vaisseau) / PV / Nombre de cartes : refletent config/modules.json tel quel.</t>
+          <t>l'ecran Vaisseau, specs.md 5) / PV / Nombre de cartes : refletent config/modules.json tel quel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>- Jouable : Oui pour les 6 modules avec des cartes (dont Principal), Non pour les 4 nouveaux</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>- Jouable : Oui pour les 6 modules avec des cartes (dont Principal), Non pour les 4 nouveaux</t>
+          <t xml:space="preserve">  (pas encore de cartes concues).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  (pas encore de cartes concues).</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
           <t>- Notes : etat d'implementation par module.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Miroir humainement modifiable, comme Cartes/Aventures/Ennemis - pas relu par le code. Voir CLAUDE.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>Nom</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="E22" s="14" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F22" s="14" t="inlineStr">
+        <is>
+          <t>Nb cartes</t>
+        </is>
+      </c>
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t>Jouable</t>
+        </is>
+      </c>
+      <c r="H22" s="14" t="inlineStr">
+        <is>
+          <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t>MOD_1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nom</t>
+          <t>Principal</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Image</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>PV</t>
-        </is>
+          <t>assets/modules/principal.png</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>50</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Description gameplay</t>
-        </is>
+          <t>Votre vaisseau, plus cabosse que le Faucon Millenium, mais la prunelle de vos yeux.</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>6</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nb cartes</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Jouable</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Notes</t>
+          <t>Module de base, toujours equipe (specs.md 5).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MOD_1</t>
+          <t>MOD_2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Principal</t>
+          <t>Lanceur de missiles</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>assets/modules/principal.png</t>
+          <t>assets/modules/missiles.png</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Votre vaisseau, plus cabosse que le Faucon Millenium, mais la prunelle de vos yeux.</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Le coeur du vaisseau : attaque directe, defense et reparation.</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>6</v>
+          <t>Tout dans la finesse, des bons vieux missiles qui explosent partout (sauf la ou vous etes, on espere).</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>3</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Module de base, toujours equipe (specs.md 5).</t>
+          <t>Implemente, cartes existantes (Ciel de missiles, Missiles groupes, Leurre).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MOD_2</t>
+          <t>MOD_3</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lanceur de missiles</t>
+          <t>Blindage</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>assets/modules/missiles.png</t>
+          <t>assets/modules/bouclier.png</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -3565,42 +3587,37 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tout dans la finesse, des bons vieux missiles qui explosent partout (sauf la ou vous etes, on espere).</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Degats de zone.</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>3</v>
+          <t>Quand la diplomatie a echoue et qu'on passe a la suite, mieux vaut pouvoir s'abriter.</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>5</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Implemente, cartes existantes (Ciel de missiles, Missiles groupes, Leurre).</t>
+          <t>Implemente, cartes existantes (Bouclier, Bouclier perpetuel, Blindage maximal, Bouclier adaptatif, Proteger l'avant poste).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MOD_3</t>
+          <t>MOD_4</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Blindage</t>
+          <t>Generateur</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>assets/modules/bouclier.png</t>
+          <t>assets/modules/generateur.png</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -3608,42 +3625,37 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Quand la diplomatie a echoue et qu'on passe a la suite, mieux vaut pouvoir s'abriter.</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Protection des modules via des boucliers.</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>5</v>
+          <t>Une eolienne dans l'espace ? Vous etes sur ?</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Implemente, cartes existantes (Bouclier, Bouclier perpetuel, Blindage maximal, Bouclier adaptatif, Proteger l'avant poste).</t>
+          <t>Implemente, cartes existantes (Surcharge temporaire, Fonds de tiroir).</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MOD_4</t>
+          <t>MOD_5</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Generateur</t>
+          <t>Soute</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>assets/modules/generateur.png</t>
+          <t>assets/modules/soute.png</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -3651,42 +3663,37 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Une eolienne dans l'espace ? Vous etes sur ?</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Manipulation de l'electricite.</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>2</v>
+          <t>Une soute bien remplie pour parer a toutes les (mauvaises) surprises...</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Implemente, cartes existantes (Surcharge temporaire, Fonds de tiroir).</t>
+          <t>Implemente, carte existante (Boost).</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MOD_5</t>
+          <t>MOD_6</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Soute</t>
+          <t>Sabotage</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>assets/modules/soute.png</t>
+          <t>assets/modules/sabotage.png</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -3694,42 +3701,37 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Une soute bien remplie pour parer a toutes les (mauvaises) surprises...</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Manipulation du deck.</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>1</v>
+          <t>Comment ca ton canon est tombe en panne ? C'est marrant parce que le mien non. Regarde...</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>6</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Implemente, carte existante (Boost).</t>
+          <t>Implemente, cartes existantes (Tordre le canon, Breche, Ligne avant, Boucliers endommages, Boucliers hors service, Tir allie).</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MOD_6</t>
+          <t>MOD_7</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Sabotage</t>
+          <t>Canon lourd</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>assets/modules/sabotage.png</t>
+          <t>assets/modules/canon_lourd.png</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -3737,42 +3739,37 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Comment ca ton canon est tombe en panne ? C'est marrant parce que le mien non. Regarde...</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Debuffs sur l'ennemi.</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>6</v>
+          <t>Ce module envoie du lourd, mieux vaut ne pas se trouver en face.</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Implemente, cartes existantes (Tordre le canon, Breche, Ligne avant, Boucliers endommages, Boucliers hors service, Tir allie).</t>
+          <t>Nouveau module (attaque a forte valeur sur cible unique) - aucune carte concue pour l'instant, exclu du tirage (modules_equipables).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MOD_7</t>
+          <t>MOD_8</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Canon lourd</t>
+          <t>Controle</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>assets/modules/canon_lourd.png</t>
+          <t>assets/modules/controle.png</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -3780,42 +3777,37 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ce module envoie du lourd, mieux vaut ne pas se trouver en face.</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Gros degats sur une cible unique.</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
+          <t>La meilleure facon de se proteger des attaques de l'ennemi, c'est encore de l'empecher de les lancer.</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
         <v>0</v>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Nouveau module (attaque a forte valeur sur cible unique) - aucune carte concue pour l'instant, exclu du tirage (modules_equipables).</t>
+          <t>Nouveau module (controle/stun de l'ennemi, specs.md 12.5 - type Controle du moteur, actuellement sans carte) - aucune carte concue, exclu du tirage.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MOD_8</t>
+          <t>MOD_9</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Controle</t>
+          <t>Atelier</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>assets/modules/controle.png</t>
+          <t>assets/modules/atelier.png</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -3823,42 +3815,37 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>La meilleure facon de se proteger des attaques de l'ennemi, c'est encore de l'empecher de les lancer.</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Controle de l'ennemi (stun...).</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
+          <t>Bricoler le vaisseau alors que ca tire de tout cote ? Meme pas peur !</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
         <v>0</v>
       </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Nouveau module (controle/stun de l'ennemi, specs.md 12.5 - type Controle du moteur, actuellement sans carte) - aucune carte concue, exclu du tirage.</t>
+          <t>Nouveau module (reparation/deplacement de modules) - aucune carte concue pour l'instant, exclu du tirage.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MOD_9</t>
+          <t>MOD_10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Atelier</t>
+          <t>Radar</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>assets/modules/atelier.png</t>
+          <t>assets/modules/radar.png</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -3866,66 +3853,18 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bricoler le vaisseau alors que ca tire de tout cote ? Meme pas peur !</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Reparation des modules. Deplacement des modules.</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
+          <t>Quand on connait les points faibles, on peut faire beaucoup plus mal.</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
         <v>0</v>
       </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Nouveau module (reparation/deplacement de modules) - aucune carte concue pour l'instant, exclu du tirage.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>MOD_10</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Radar</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>assets/modules/radar.png</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>30</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Quand on connait les points faibles, on peut faire beaucoup plus mal.</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Buffs sur les modules du joueur.</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
         <is>
           <t>Nouveau module (buffs sur les modules du joueur) - aucune carte concue pour l'instant, exclu du tirage.</t>
         </is>

--- a/specs/cartes.xlsx
+++ b/specs/cartes.xlsx
@@ -824,7 +824,11 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L5" s="4" t="inlineStr"/>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>Retiree du module principal (decision utilisateur, deck de base 12-&gt;10 cartes) : sera reintroduite sous une forme modifiee comme carte du Lanceur de missiles - pas encore prete (config/modules.json ne reference plus cet id pour l'instant).</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -972,7 +976,11 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L8" s="4" t="inlineStr"/>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>Retiree du module principal (decision utilisateur, deck de base 12-&gt;10 cartes) : sera reintroduite comme carte de l'Atelier - pas encore prete (config/modules.json ne reference plus cet id pour l'instant).</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -3515,7 +3523,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -3524,7 +3532,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Module de base, toujours equipe (specs.md 5).</t>
+          <t>Module de base, toujours equipe (specs.md 5). Bombardement et Reparation retires du deck de base (decision utilisateur, deck de 12 a 10 cartes) : Bombardement redeviendra une carte du Lanceur de missiles (forme modifiee), Reparation une carte de l'Atelier - aucun des deux n'est encore pret.</t>
         </is>
       </c>
     </row>

--- a/specs/cartes.xlsx
+++ b/specs/cartes.xlsx
@@ -779,12 +779,12 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Commune</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Module principal</t>
+          <t>Lanceur de missiles</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" s="4" t="n">
         <v>3</v>
@@ -826,7 +826,7 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>Retiree du module principal (decision utilisateur, deck de base 12-&gt;10 cartes) : sera reintroduite sous une forme modifiee comme carte du Lanceur de missiles - pas encore prete (config/modules.json ne reference plus cet id pour l'instant).</t>
+          <t>Deplacee du module principal vers le Lanceur de missiles (decision utilisateur, deck de base 12-&gt;10 cartes). Rarete Base-&gt;Commune, cout 2-&gt;1, X inchange.</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Commune</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -1151,7 +1151,11 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="L12" s="4" t="inlineStr"/>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>Rarete Commune-&gt;Rare (arrivee de Bombardement dans le module, decision utilisateur).</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -1175,10 +1179,10 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G13" s="4" t="n"/>
       <c r="H13" s="4" t="inlineStr">
@@ -1198,12 +1202,12 @@
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>cible 'ennemis de la ligne arriere' non representable par CibleCarte (voir specs.md 9.1)</t>
+          <t>Cout 2-&gt;1, X 7-&gt;6 (arrivee de Bombardement dans le module, decision utilisateur). Correction : cette carte est en fait deja jouable (CibleCarte.COLONNE_ARRIERE_ENNEMIE implemente dans combat.py) - l'ancienne note (cible non representable) etait perimee.</t>
         </is>
       </c>
     </row>
@@ -3532,7 +3536,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Module de base, toujours equipe (specs.md 5). Bombardement et Reparation retires du deck de base (decision utilisateur, deck de 12 a 10 cartes) : Bombardement redeviendra une carte du Lanceur de missiles (forme modifiee), Reparation une carte de l'Atelier - aucun des deux n'est encore pret.</t>
+          <t>Module de base, toujours equipe (specs.md 5). Bombardement et Reparation retires du deck de base (decision utilisateur, deck de 12 a 10 cartes) : Bombardement a rejoint le Lanceur de missiles (forme modifiee), Reparation deviendra une carte de l'Atelier - pas encore pret.</t>
         </is>
       </c>
     </row>
@@ -3561,7 +3565,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -3570,7 +3574,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Implemente, cartes existantes (Ciel de missiles, Missiles groupes, Leurre).</t>
+          <t>Implemente, cartes existantes (Missiles, Torpille, Ciel de missiles, Ligne arriere, Embrasement, Leurre, Guerre nucleaire), dont 4 jouables actuellement equipables (Ciel de missiles, Ligne arriere, Leurre, Bombardement). Bombardement (ex-module principal) rejoint ce module (decision utilisateur).</t>
         </is>
       </c>
     </row>

--- a/specs/cartes.xlsx
+++ b/specs/cartes.xlsx
@@ -2947,7 +2947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2973,7 +2973,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Transcrit depuis une capture d'ecran fournie par l'utilisateur (tableau de conception des ennemis) - a remplace les 3 ennemis placeholder de config/ennemis.json (ENM_1/2/3, simple "attaque unique X degats", cf. specs.md 3.2). Desormais implemente (specs.md 13, config/ennemis.json) : les 5 ennemis ci-dessous sont les seuls du jeu.</t>
+          <t>Transcrit depuis une capture d'ecran fournie par l'utilisateur (tableau de conception des ennemis) - a remplace les 3 ennemis placeholder de config/ennemis.json (ENM_1/2/3, simple "attaque unique X degats", cf. specs.md 3.2). Desormais implemente (specs.md 13, config/ennemis.json). Le Boss des pirates (ligne 26) a ete ajoute separement (boss du niveau 10, fourni par l'utilisateur) : 6 ennemis au total desormais.</t>
         </is>
       </c>
     </row>
@@ -3338,6 +3338,56 @@
       <c r="K25" s="12" t="inlineStr">
         <is>
           <t>Implemente : ActionCarte.BOUCLIER_MIROIR (nouveau type de buff, cf. carte.py) pose sur un module tire au hasard en colonne avant sinon arriere (CibleActionEnnemi.COLONNE_AVANT_SINON_ARRIERE_JOUEUR). Renvoi de degats implemente dans Combat._resoudre_attaque/_consommer_bouclier_miroir : jusqu'a la valeur du bouclier miroir est retiree a l'attaquant, le reste s'applique normalement a la cible - le dernier chiffre de l'exemple, complete par calcul lors de la transcription (8-5=3), est confirme correct par l'implementation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Le Boss des pirates</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>assets/ennemis/boss_pirates.png</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>On ne rigole pas trop avec le boss et son cigare lance-torpille !</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>150</v>
+      </c>
+      <c r="F26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Inflige X degats a tous les modules du joueur, a chaque tour.
+A partir du tour 2, tous les 3 tours : augmente ses degats d'attaque de 2 (cumulatif, permanent).
+A partir du tour 3, tous les 3 tours : se pose un bouclier de 5.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Occupe 2 emplacements (une case Avant + une case Arriere de la meme rangee) - premier ennemi a plusieurs emplacements du jeu (specs.md 3.2). Boss du niveau 10 (et de tous les niveaux Boss suivants pour l'instant, decision utilisateur) - un seul boss existe a ce stade, plusieurs avec tirage au sort entre eux sont prevus a terme.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Implemente : ActionCarte.AUGMENTATION_DEGATS (nouveau type de buff, symetrique de REDUCTION_DEGATS) ajoute a Ennemi.degats_attaque_effectifs. Ennemi.emplacements (nouveau champ, config/ennemis.json) fait occuper 2 Positions a la fois dans Flotte (meme objet range aux deux cases) - Flotte.ennemis_vivants()/positions_de() et plusieurs verifications de Combat (ciblage colonne/ligne, tour ennemi) adaptees pour ne jamais le toucher/faire jouer deux fois. Reserve aux flottes scriptees (config_poc.creer_flotte_boss, qui remplace l'ancienne composition a 4 ennemis - 2 Petit Jean + Nettoyeur + Puzzle), exclu du tirage au hasard des combats Prime/demonstration/Asteroides (_pool_ennemis_standard). Rendu PC/web : case fusionnee sur les 2 emplacements plutot que deux sprites/PV dupliques (specs.md 3.2, §9.1 - question ouverte tranchee par ce choix). Image boss_pirates.png : placeholder genere automatiquement en attendant l'asset final de l'utilisateur.</t>
         </is>
       </c>
     </row>

--- a/specs/cartes.xlsx
+++ b/specs/cartes.xlsx
@@ -3313,21 +3313,21 @@
         <v>50</v>
       </c>
       <c r="F25" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" t="n">
         <v>5</v>
       </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
       <c r="H25" s="12" t="inlineStr">
         <is>
-          <t>Pose un "bouclier miroir" de X sur un ennemi de la ligne avant si possible, de la ligne arriere sinon.
-Bouclier miroir = les degats d'un ennemi jusqu'a X lui sont renvoyes (la cible ne subit rien, l'attaquant subit X). Les degats au-dela de X sont geres normalement.
-Exemple bouclier miroir de 5, attaque par M de E pour 8 : M subit 5, E subit 3.</t>
+          <t>Inflige X degats en face de lui.
+Pose un bouclier miroir de Y sur un ennemi de la ligne avant si possible, de la ligne arriere sinon (lui-meme y compris).
+Bouclier miroir = les degats d'une attaque du JOUEUR jusqu'a Y sont renvoyes (la cible protegee ne subit rien pour cette part). Les degats au-dela de Y s'appliquent normalement a la cible.</t>
         </is>
       </c>
       <c r="I25" s="12" t="inlineStr">
         <is>
-          <t>Aucune</t>
+          <t>Peut se cibler lui-meme (aucun autre ennemi vivant, ou tire au sort).</t>
         </is>
       </c>
       <c r="J25" s="13" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="K25" s="12" t="inlineStr">
         <is>
-          <t>Implemente : ActionCarte.BOUCLIER_MIROIR (nouveau type de buff, cf. carte.py) pose sur un module tire au hasard en colonne avant sinon arriere (CibleActionEnnemi.COLONNE_AVANT_SINON_ARRIERE_JOUEUR). Renvoi de degats implemente dans Combat._resoudre_attaque/_consommer_bouclier_miroir : jusqu'a la valeur du bouclier miroir est retiree a l'attaquant, le reste s'applique normalement a la cible - le dernier chiffre de l'exemple, complete par calcul lors de la transcription (8-5=3), est confirme correct par l'implementation.</t>
+          <t>Implemente : cible changee de 'un module du joueur' (version initiale de la transcription) vers 'un ennemi allie' (decision utilisateur), conformement au texte d'origine de cette colonne qui le decrivait deja ainsi - CibleActionEnnemi.COLONNE_AVANT_SINON_ARRIERE_ENNEMIE (nouvelle valeur, remplace COLONNE_AVANT_SINON_ARRIERE_JOUEUR pour Miroir, conservee pour un futur ennemi). Nouvelle attaque de proximite (2 degats/tour, meme mecanique que Pat le Pirate) ajoutee a la demande de l'utilisateur, absente de la transcription initiale. Renvoi de degats : deux mecanismes distincts selon qui attaque l'ennemi protege (specs.md 13.2) - une Action ennemie (ex. Tir allie) renvoie a l'attaquant reel (Combat._consommer_bouclier_miroir/_resoudre_attaque, inchange) ; une carte jouee par le JOUEUR n'a pas d'attaquant identifiable, donc renvoie vers un module du joueur tire au hasard UNE SEULE FOIS a la pose du buff plutot qu'a la resolution (BuffActif.cible_reflet, Combat._executer_pose_buff/_consommer_bouclier_miroir_vers_joueur) - affiche des la pose dans l'infobulle de l'ennemi protege pour que le joueur puisse anticiper.</t>
         </is>
       </c>
     </row>
